--- a/data/trans_dic/IP04D$aparatos-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP04D$aparatos-Clase-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -521,8 +522,10 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="n">
-        <v/>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>nan (tasa de respuesta: 99,64%)</t>
+        </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
@@ -675,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>40,37; 56,97</t>
+          <t>40,98; 57,85</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>35,14; 52,46</t>
+          <t>34,35; 51,65</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>39,97; 57,29</t>
+          <t>41,28; 57,12</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>36,82; 53,57</t>
+          <t>37,92; 55,53</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>35,21; 51,92</t>
+          <t>35,23; 51,82</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>33,92; 51,47</t>
+          <t>34,32; 50,94</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>41,75; 53,95</t>
+          <t>41,3; 53,87</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>37,3; 49,45</t>
+          <t>37,75; 49,92</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>39,08; 51,34</t>
+          <t>39,02; 51,39</t>
         </is>
       </c>
     </row>
@@ -785,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>48,6; 64,96</t>
+          <t>47,78; 65,15</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>44,21; 60,16</t>
+          <t>43,69; 60,87</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>48,25; 64,93</t>
+          <t>48,39; 65,02</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>40,24; 57,98</t>
+          <t>40,76; 56,91</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>35,59; 50,73</t>
+          <t>35,57; 50,81</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>47,79; 64,98</t>
+          <t>47,47; 65,44</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>46,97; 58,21</t>
+          <t>47,34; 59,14</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>41,33; 52,64</t>
+          <t>41,6; 53,11</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>50,61; 63,04</t>
+          <t>50,42; 62,55</t>
         </is>
       </c>
     </row>
@@ -895,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>56,49; 73,87</t>
+          <t>56,83; 73,26</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>43,98; 65,24</t>
+          <t>44,63; 63,84</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>51,0; 73,54</t>
+          <t>51,33; 72,84</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>57,23; 73,18</t>
+          <t>57,4; 74,08</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>40,17; 60,09</t>
+          <t>40,08; 58,69</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>53,52; 75,82</t>
+          <t>52,76; 75,66</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>59,54; 71,36</t>
+          <t>59,4; 72,15</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>44,53; 58,49</t>
+          <t>44,96; 58,52</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>57,29; 71,9</t>
+          <t>56,71; 72,65</t>
         </is>
       </c>
     </row>
@@ -1005,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>63,28; 74,43</t>
+          <t>64,03; 74,51</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>45,34; 56,25</t>
+          <t>45,02; 55,73</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>56,13; 77,2</t>
+          <t>55,92; 77,5</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>56,08; 67,28</t>
+          <t>56,71; 67,45</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>50,68; 62,84</t>
+          <t>50,87; 62,21</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>53,87; 67,17</t>
+          <t>53,68; 66,66</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>62,13; 69,51</t>
+          <t>61,61; 69,43</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>49,3; 57,14</t>
+          <t>49,56; 57,37</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>57,62; 69,75</t>
+          <t>57,31; 70,12</t>
         </is>
       </c>
     </row>
@@ -1115,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>60,64; 73,34</t>
+          <t>60,54; 73,02</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>58,2; 71,21</t>
+          <t>57,69; 70,95</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>62,05; 76,22</t>
+          <t>61,93; 76,57</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>60,83; 74,18</t>
+          <t>59,99; 73,6</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>55,11; 68,67</t>
+          <t>55,03; 69,03</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>49,47; 72,39</t>
+          <t>50,76; 72,4</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>62,55; 71,9</t>
+          <t>62,64; 71,56</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>58,35; 68,08</t>
+          <t>58,13; 67,72</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>56,96; 71,99</t>
+          <t>56,85; 72,16</t>
         </is>
       </c>
     </row>
@@ -1225,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>61,77; 83,1</t>
+          <t>62,59; 82,85</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>39,35; 60,68</t>
+          <t>40,4; 61,39</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>57,49; 78,76</t>
+          <t>58,74; 79,09</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>63,54; 80,37</t>
+          <t>63,03; 80,09</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>46,78; 65,39</t>
+          <t>45,63; 65,78</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>59,25; 79,22</t>
+          <t>59,01; 79,36</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>66,07; 79,03</t>
+          <t>66,53; 79,23</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>45,73; 60,29</t>
+          <t>45,83; 60,63</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>61,85; 76,02</t>
+          <t>61,27; 75,98</t>
         </is>
       </c>
     </row>
@@ -1335,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>61,18; 67,17</t>
+          <t>61,31; 67,36</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>49,79; 55,98</t>
+          <t>49,71; 55,93</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>58,3; 67,7</t>
+          <t>58,36; 67,07</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>58,06; 64,13</t>
+          <t>57,74; 64,06</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>50,09; 56,3</t>
+          <t>49,66; 55,96</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>54,85; 62,64</t>
+          <t>54,8; 62,42</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>60,41; 64,7</t>
+          <t>60,46; 64,76</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>50,64; 55,35</t>
+          <t>50,63; 55,13</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>57,72; 63,71</t>
+          <t>58,02; 64,1</t>
         </is>
       </c>
     </row>
@@ -1402,4 +1405,1283 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>nan (tasa de respuesta: 99,64%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Grupo I y II</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>157</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>44218</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>35999</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>50791</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>41230</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>43512</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>58269</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>85448</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>79511</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>109059</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>36851; 52023</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>28543; 42919</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>43125; 59673</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>34042; 49843</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>34895; 51326</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>46417; 68896</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>74222; 96802</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>68750; 90912</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>93549; 123197</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Grupo III</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>147</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>148</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>158</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>52712</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>54080</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>53919</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>47345</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>48154</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>54173</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100058</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>102234</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>108092</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>44182; 60247</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>45621; 63566</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>45813; 61564</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>39451; 55078</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>39870; 56945</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>45373; 62541</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>89592; 111926</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>90054; 114992</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>95935; 119011</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Grupo IV y V</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>166</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>56780</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>33446</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>32747</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>57262</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>36984</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>41794</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>114043</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>70431</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>74541</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>48965; 63120</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>27597; 39479</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>26621; 37774</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>49873; 64365</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>29974; 43889</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>33688; 48313</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>102797; 124850</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>61425; 79946</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>65621; 84064</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>172</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>177</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>203</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>169</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>412</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>341</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>356</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>143013</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>112828</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>141168</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>141873</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>118242</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>132722</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>284886</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>231070</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>273889</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>131968; 153567</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>100659; 124607</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>121810; 168814</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>129008; 153427</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>106189; 129868</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>117160; 145503</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>267124; 301052</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>214268; 248049</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>249934; 305802</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VII</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>271</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>254</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>266</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>99305</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>87764</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>83155</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>94798</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>88368</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>104738</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>194104</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>176131</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>187893</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>89334; 107750</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>78192; 96163</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>73966; 91447</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>84233; 103333</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>78377; 98314</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>82540; 117742</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>180372; 206059</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>161588; 188232</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>160349; 203510</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>135</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>39143</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>30574</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>47654</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>53768</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>38015</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>49998</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>92911</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>68589</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>97652</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>33307; 44092</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>24676; 37500</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>40472; 54491</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>46668; 59296</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>30951; 44617</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>42490; 57138</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>84663; 100831</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>59082; 78164</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>86333; 107053</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>632</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>528</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>579</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>624</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>536</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>593</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>1256</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>1064</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>1172</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>435172</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>354691</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>409433</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>436278</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>373275</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>441693</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>871450</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>727966</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>851125</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>414087; 454984</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>332827; 374490</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>383534; 440750</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>413043; 458247</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>350049; 394476</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>409663; 466622</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>840833; 900626</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>695846; 757728</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>815047; 900452</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP04D$aparatos-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP04D$aparatos-Clase-trans_dic.xlsx
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>40,98; 57,85</t>
+          <t>41,13; 57,99</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>34,35; 51,65</t>
+          <t>34,59; 53,1</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>41,28; 57,12</t>
+          <t>40,28; 56,78</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>37,92; 55,53</t>
+          <t>37,82; 54,09</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>35,23; 51,82</t>
+          <t>35,54; 52,21</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>34,32; 50,94</t>
+          <t>33,98; 51,89</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>41,3; 53,87</t>
+          <t>41,17; 54,12</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>37,75; 49,92</t>
+          <t>37,88; 49,53</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>39,02; 51,39</t>
+          <t>39,28; 51,18</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>47,78; 65,15</t>
+          <t>47,93; 65,07</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>43,69; 60,87</t>
+          <t>43,65; 59,81</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>48,39; 65,02</t>
+          <t>48,22; 65,29</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>40,76; 56,91</t>
+          <t>40,73; 57,02</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>35,57; 50,81</t>
+          <t>35,77; 50,8</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>47,47; 65,44</t>
+          <t>47,51; 64,98</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>47,34; 59,14</t>
+          <t>46,54; 58,48</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>41,6; 53,11</t>
+          <t>41,89; 52,7</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>50,42; 62,55</t>
+          <t>50,9; 62,7</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>56,83; 73,26</t>
+          <t>56,29; 74,09</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>44,63; 63,84</t>
+          <t>44,22; 63,75</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>51,33; 72,84</t>
+          <t>51,32; 74,17</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>57,4; 74,08</t>
+          <t>57,27; 74,15</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>40,08; 58,69</t>
+          <t>39,6; 59,06</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>52,76; 75,66</t>
+          <t>53,27; 75,78</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>59,4; 72,15</t>
+          <t>60,0; 71,34</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>44,96; 58,52</t>
+          <t>44,5; 58,85</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>56,71; 72,65</t>
+          <t>56,76; 72,46</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>64,03; 74,51</t>
+          <t>63,9; 74,18</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>45,02; 55,73</t>
+          <t>45,28; 56,24</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>55,92; 77,5</t>
+          <t>56,86; 78,5</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>56,71; 67,45</t>
+          <t>56,73; 67,48</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>50,87; 62,21</t>
+          <t>50,79; 62,39</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>53,68; 66,66</t>
+          <t>53,65; 67,34</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>61,61; 69,43</t>
+          <t>61,87; 69,55</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>49,56; 57,37</t>
+          <t>49,78; 57,37</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>57,31; 70,12</t>
+          <t>57,86; 70,29</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>60,54; 73,02</t>
+          <t>60,78; 72,92</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>57,69; 70,95</t>
+          <t>58,29; 71,73</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>61,93; 76,57</t>
+          <t>62,25; 76,14</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>59,99; 73,6</t>
+          <t>59,99; 74,02</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>55,03; 69,03</t>
+          <t>54,45; 68,45</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>50,76; 72,4</t>
+          <t>50,4; 72,89</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>62,64; 71,56</t>
+          <t>62,29; 72,08</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>58,13; 67,72</t>
+          <t>58,64; 68,03</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>56,85; 72,16</t>
+          <t>57,9; 72,41</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>62,59; 82,85</t>
+          <t>62,17; 82,31</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>40,4; 61,39</t>
+          <t>40,18; 60,59</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>58,74; 79,09</t>
+          <t>58,81; 79,7</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>63,03; 80,09</t>
+          <t>63,44; 80,5</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>45,63; 65,78</t>
+          <t>46,15; 65,77</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>59,01; 79,36</t>
+          <t>58,9; 78,75</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>66,53; 79,23</t>
+          <t>66,7; 79,42</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>45,83; 60,63</t>
+          <t>46,08; 60,46</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>61,27; 75,98</t>
+          <t>61,62; 75,85</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>61,31; 67,36</t>
+          <t>61,64; 67,26</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>49,71; 55,93</t>
+          <t>49,93; 56,25</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>58,36; 67,07</t>
+          <t>58,32; 67,3</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>57,74; 64,06</t>
+          <t>57,97; 63,75</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>49,66; 55,96</t>
+          <t>50,06; 56,39</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>54,8; 62,42</t>
+          <t>55,14; 62,8</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>60,46; 64,76</t>
+          <t>60,53; 64,7</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>50,63; 55,13</t>
+          <t>50,58; 55,17</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>58,02; 64,1</t>
+          <t>57,94; 63,62</t>
         </is>
       </c>
     </row>
@@ -1639,47 +1639,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>36851; 52023</t>
+          <t>36989; 52148</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>28543; 42919</t>
+          <t>28738; 44120</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>43125; 59673</t>
+          <t>42082; 59317</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>34042; 49843</t>
+          <t>33944; 48556</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>34895; 51326</t>
+          <t>35203; 51712</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>46417; 68896</t>
+          <t>45964; 70181</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>74222; 96802</t>
+          <t>73980; 97247</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>68750; 90912</t>
+          <t>68983; 90205</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>93549; 123197</t>
+          <t>94160; 122679</t>
         </is>
       </c>
     </row>
@@ -1802,47 +1802,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>44182; 60247</t>
+          <t>44319; 60177</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>45621; 63566</t>
+          <t>45579; 62450</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>45813; 61564</t>
+          <t>45655; 61818</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>39451; 55078</t>
+          <t>39413; 55185</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>39870; 56945</t>
+          <t>40089; 56939</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>45373; 62541</t>
+          <t>45402; 62105</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>89592; 111926</t>
+          <t>88072; 110682</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>90054; 114992</t>
+          <t>90691; 114091</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>95935; 119011</t>
+          <t>96840; 119284</t>
         </is>
       </c>
     </row>
@@ -1965,47 +1965,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>48965; 63120</t>
+          <t>48496; 63830</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>27597; 39479</t>
+          <t>27345; 39423</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>26621; 37774</t>
+          <t>26614; 38465</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>49873; 64365</t>
+          <t>49764; 64425</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>29974; 43889</t>
+          <t>29614; 44169</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>33688; 48313</t>
+          <t>34013; 48389</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>102797; 124850</t>
+          <t>103826; 123452</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>61425; 79946</t>
+          <t>60796; 80405</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>65621; 84064</t>
+          <t>65676; 83843</t>
         </is>
       </c>
     </row>
@@ -2128,47 +2128,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>131968; 153567</t>
+          <t>131702; 152882</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>100659; 124607</t>
+          <t>101247; 125747</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>121810; 168814</t>
+          <t>123857; 170999</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>129008; 153427</t>
+          <t>129051; 153498</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>106189; 129868</t>
+          <t>106021; 130248</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>117160; 145503</t>
+          <t>117105; 146985</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>267124; 301052</t>
+          <t>268259; 301564</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>214268; 248049</t>
+          <t>215222; 248021</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>249934; 305802</t>
+          <t>252328; 306527</t>
         </is>
       </c>
     </row>
@@ -2291,47 +2291,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>89334; 107750</t>
+          <t>89678; 107596</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>78192; 96163</t>
+          <t>79006; 97211</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>73966; 91447</t>
+          <t>74341; 90932</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>84233; 103333</t>
+          <t>84225; 103924</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>78377; 98314</t>
+          <t>77542; 97495</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>82540; 117742</t>
+          <t>81959; 118535</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>180372; 206059</t>
+          <t>179382; 207556</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>161588; 188232</t>
+          <t>162990; 189096</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>160349; 203510</t>
+          <t>163290; 204236</t>
         </is>
       </c>
     </row>
@@ -2454,47 +2454,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>33307; 44092</t>
+          <t>33082; 43802</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>24676; 37500</t>
+          <t>24543; 37013</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>40472; 54491</t>
+          <t>40517; 54912</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>46668; 59296</t>
+          <t>46972; 59598</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>30951; 44617</t>
+          <t>31298; 44610</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>42490; 57138</t>
+          <t>42412; 56704</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>84663; 100831</t>
+          <t>84885; 101071</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>59082; 78164</t>
+          <t>59408; 77940</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>86333; 107053</t>
+          <t>86817; 106875</t>
         </is>
       </c>
     </row>
@@ -2617,47 +2617,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>414087; 454984</t>
+          <t>416347; 454272</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>332827; 374490</t>
+          <t>334324; 376590</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>383534; 440750</t>
+          <t>383252; 442254</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>413043; 458247</t>
+          <t>414658; 456071</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>350049; 394476</t>
+          <t>352865; 397513</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>409663; 466622</t>
+          <t>412248; 469504</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>840833; 900626</t>
+          <t>841834; 899829</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>695846; 757728</t>
+          <t>695222; 758317</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>815047; 900452</t>
+          <t>813924; 893701</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP04D$aparatos-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP04D$aparatos-Clase-trans_dic.xlsx
@@ -524,20 +524,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>nan (tasa de respuesta: 99,64%)</t>
+          <t>Población que no dispone de instalación de calefacción en su vivienda pero sí tiene aparatos de calefacción (tasa de respuesta: 99,64%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -625,32 +625,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>45,93%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>43,93%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>47,01%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>49,17%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>43,33%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>48,62%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>45,93%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>43,93%</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>43,08%</t>
+          <t>47,84%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>45,49%</t>
+          <t>47,39%</t>
         </is>
       </c>
     </row>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>41,13; 57,99</t>
+          <t>36,82; 53,57</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>34,59; 53,1</t>
+          <t>35,21; 51,92</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>40,28; 56,78</t>
+          <t>38,63; 54,67</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>37,82; 54,09</t>
+          <t>40,37; 56,97</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>35,54; 52,21</t>
+          <t>35,14; 52,46</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>33,98; 51,89</t>
+          <t>39,24; 56,14</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>41,17; 54,12</t>
+          <t>41,75; 53,95</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>37,88; 49,53</t>
+          <t>37,3; 49,45</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>39,28; 51,18</t>
+          <t>41,33; 52,94</t>
         </is>
       </c>
     </row>
@@ -735,32 +735,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>48,92%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>42,97%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>57,39%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>57,0%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>51,79%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>56,95%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>48,92%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>42,97%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>56,68%</t>
+          <t>57,79%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>56,81%</t>
+          <t>57,6%</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>47,93; 65,07</t>
+          <t>40,24; 57,98</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>43,65; 59,81</t>
+          <t>35,59; 50,73</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>48,22; 65,29</t>
+          <t>48,08; 65,67</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>40,73; 57,02</t>
+          <t>48,6; 64,96</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>35,77; 50,8</t>
+          <t>44,21; 60,16</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>47,51; 64,98</t>
+          <t>48,95; 65,88</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>46,54; 58,48</t>
+          <t>46,97; 58,21</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>41,89; 52,7</t>
+          <t>41,33; 52,64</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>50,9; 62,7</t>
+          <t>51,2; 63,68</t>
         </is>
       </c>
     </row>
@@ -850,34 +850,34 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
+          <t>49,46%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>67,46%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>65,9%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>54,09%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>63,14%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>64,51%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>65,9%</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>49,46%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>65,45%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>65,9%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
           <t>51,55%</t>
@@ -885,7 +885,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>64,42%</t>
+          <t>66,03%</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>56,29; 74,09</t>
+          <t>57,23; 73,18</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>44,22; 63,75</t>
+          <t>40,17; 60,09</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>51,32; 74,17</t>
+          <t>56,72; 77,77</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>57,27; 74,15</t>
+          <t>56,49; 73,87</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>39,6; 59,06</t>
+          <t>43,98; 65,24</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>53,27; 75,78</t>
+          <t>52,76; 74,64</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>60,0; 71,34</t>
+          <t>59,54; 71,36</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>44,5; 58,85</t>
+          <t>44,53; 58,49</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>56,76; 72,46</t>
+          <t>59,06; 73,68</t>
         </is>
       </c>
     </row>
@@ -955,32 +955,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>62,37%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>56,64%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>60,72%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>69,39%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>50,46%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>64,81%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>62,37%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>56,64%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>60,81%</t>
+          <t>63,47%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>62,8%</t>
+          <t>62,01%</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>63,9; 74,18</t>
+          <t>56,08; 67,28</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>45,28; 56,24</t>
+          <t>50,68; 62,84</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>56,86; 78,5</t>
+          <t>53,65; 67,4</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>56,73; 67,48</t>
+          <t>63,28; 74,43</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>50,79; 62,39</t>
+          <t>45,34; 56,25</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>53,65; 67,34</t>
+          <t>57,13; 69,13</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>61,87; 69,55</t>
+          <t>62,13; 69,51</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>49,78; 57,37</t>
+          <t>49,3; 57,14</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>57,86; 70,29</t>
+          <t>57,64; 66,29</t>
         </is>
       </c>
     </row>
@@ -1065,32 +1065,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>67,52%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>62,05%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>66,02%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>67,3%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>64,76%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>69,63%</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>67,52%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>62,05%</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>64,41%</t>
+          <t>70,03%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>66,62%</t>
+          <t>67,81%</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>60,78; 72,92</t>
+          <t>60,83; 74,18</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>58,29; 71,73</t>
+          <t>55,11; 68,67</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>62,25; 76,14</t>
+          <t>52,15; 73,53</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>59,99; 74,02</t>
+          <t>60,64; 73,34</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>54,45; 68,45</t>
+          <t>58,2; 71,21</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>50,4; 72,89</t>
+          <t>62,23; 76,36</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>62,29; 72,08</t>
+          <t>62,55; 71,9</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>58,64; 68,03</t>
+          <t>58,35; 68,08</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>57,9; 72,41</t>
+          <t>59,26; 72,75</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>72,62%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>56,05%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>70,65%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>73,55%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>50,05%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>69,17%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>72,62%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>56,05%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>69,44%</t>
+          <t>70,48%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>69,31%</t>
+          <t>70,57%</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>62,17; 82,31</t>
+          <t>63,54; 80,37</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>40,18; 60,59</t>
+          <t>46,78; 65,39</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>58,81; 79,7</t>
+          <t>60,33; 80,24</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>63,44; 80,5</t>
+          <t>61,77; 83,1</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>46,15; 65,77</t>
+          <t>39,35; 60,68</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>58,9; 78,75</t>
+          <t>59,03; 79,71</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>66,7; 79,42</t>
+          <t>66,07; 79,03</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>46,08; 60,46</t>
+          <t>45,73; 60,29</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>61,62; 75,85</t>
+          <t>63,23; 77,16</t>
         </is>
       </c>
     </row>
@@ -1285,32 +1285,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>60,99%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>52,95%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>60,55%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>64,43%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>52,97%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>62,3%</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>60,99%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>52,95%</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>59,08%</t>
+          <t>62,14%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>60,59%</t>
+          <t>61,3%</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>61,64; 67,26</t>
+          <t>58,06; 64,13</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>49,93; 56,25</t>
+          <t>50,09; 56,3</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>58,32; 67,3</t>
+          <t>56,58; 63,84</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>57,97; 63,75</t>
+          <t>61,18; 67,17</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>50,06; 56,39</t>
+          <t>49,79; 55,98</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>55,14; 62,8</t>
+          <t>58,77; 65,34</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>60,53; 64,7</t>
+          <t>60,41; 64,7</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>50,58; 55,17</t>
+          <t>50,64; 55,35</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>57,94; 63,62</t>
+          <t>58,72; 63,62</t>
         </is>
       </c>
     </row>
@@ -1432,20 +1432,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>nan (tasa de respuesta: 99,64%)</t>
+          <t>Población que no dispone de instalación de calefacción en su vivienda pero sí tiene aparatos de calefacción (tasa de respuesta: 99,64%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1533,32 +1533,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>66</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>52</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>78</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>79</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -1586,32 +1586,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>41230</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>43512</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>56887</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>44218</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>35999</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>50791</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>41230</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>43512</t>
-        </is>
-      </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>58269</t>
+          <t>49241</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1626,7 +1626,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>109059</t>
+          <t>106128</t>
         </is>
       </c>
     </row>
@@ -1639,47 +1639,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>36989; 52148</t>
+          <t>33049; 48086</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>28738; 44120</t>
+          <t>34875; 51424</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>42082; 59317</t>
+          <t>46738; 66147</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>33944; 48556</t>
+          <t>36305; 51239</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>35203; 51712</t>
+          <t>29200; 43587</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>45964; 70181</t>
+          <t>40393; 57786</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>73980; 97247</t>
+          <t>75015; 96938</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>68983; 90205</t>
+          <t>67929; 90065</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>94160; 122679</t>
+          <t>92546; 118555</t>
         </is>
       </c>
     </row>
@@ -1696,32 +1696,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>78</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>77</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>82</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>76</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1749,32 +1749,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>47345</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>48154</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>52449</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>52712</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>54080</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>53919</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>47345</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>48154</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>54173</t>
+          <t>55798</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>108092</t>
+          <t>108247</t>
         </is>
       </c>
     </row>
@@ -1802,47 +1802,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>44319; 60177</t>
+          <t>38944; 56111</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>45579; 62450</t>
+          <t>39890; 56859</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>45655; 61818</t>
+          <t>43946; 60023</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>39413; 55185</t>
+          <t>44943; 60069</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>40089; 56939</t>
+          <t>46161; 62817</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>45402; 62105</t>
+          <t>47260; 63606</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>88072; 110682</t>
+          <t>88884; 110161</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>90691; 114091</t>
+          <t>89486; 113962</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>96840; 119284</t>
+          <t>96235; 119689</t>
         </is>
       </c>
     </row>
@@ -1864,27 +1864,27 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>51</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>46</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1912,32 +1912,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>57262</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>36984</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>38414</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
           <t>56780</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>33446</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>32747</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>57262</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>36984</t>
-        </is>
-      </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>41794</t>
+          <t>34501</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>74541</t>
+          <t>72915</t>
         </is>
       </c>
     </row>
@@ -1965,47 +1965,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>48496; 63830</t>
+          <t>49728; 63585</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>27345; 39423</t>
+          <t>30041; 44937</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>26614; 38465</t>
+          <t>32299; 44286</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>49764; 64425</t>
+          <t>48668; 63644</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>29614; 44169</t>
+          <t>27200; 40346</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>34013; 48389</t>
+          <t>28217; 39919</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>103826; 123452</t>
+          <t>103024; 123495</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>60796; 80405</t>
+          <t>60832; 79906</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>65676; 83843</t>
+          <t>65220; 81365</t>
         </is>
       </c>
     </row>
@@ -2022,32 +2022,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>203</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>169</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
           <t>209</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>172</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>177</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>203</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>169</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>179</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -2075,32 +2075,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>141873</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>118242</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>122620</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>143013</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>112828</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>141168</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>141873</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>118242</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>132722</t>
+          <t>113346</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>273889</t>
+          <t>235967</t>
         </is>
       </c>
     </row>
@@ -2128,47 +2128,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>131702; 152882</t>
+          <t>127581; 153053</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>101247; 125747</t>
+          <t>105795; 131184</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>123857; 170999</t>
+          <t>108346; 136105</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>129051; 153498</t>
+          <t>130435; 153411</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>106021; 130248</t>
+          <t>101365; 125761</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>117105; 146985</t>
+          <t>102030; 123453</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>268259; 301564</t>
+          <t>269377; 301388</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>215222; 248021</t>
+          <t>213124; 247038</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>252328; 306527</t>
+          <t>219336; 252240</t>
         </is>
       </c>
     </row>
@@ -2185,32 +2185,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>140</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>132</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>125</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>131</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>122</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>141</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2238,32 +2238,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>94798</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>88368</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>97872</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
           <t>99305</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>87764</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>83155</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>94798</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>88368</t>
-        </is>
-      </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>104738</t>
+          <t>83153</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2278,7 +2278,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>187893</t>
+          <t>181024</t>
         </is>
       </c>
     </row>
@@ -2291,47 +2291,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>89678; 107596</t>
+          <t>85407; 104154</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>79006; 97211</t>
+          <t>78494; 97809</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>74341; 90932</t>
+          <t>77308; 109007</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>84225; 103924</t>
+          <t>89478; 108210</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>77542; 97495</t>
+          <t>78885; 96518</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>81959; 118535</t>
+          <t>73891; 90663</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>179382; 207556</t>
+          <t>180124; 207039</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>162990; 189096</t>
+          <t>162184; 189232</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>163290; 204236</t>
+          <t>158206; 194223</t>
         </is>
       </c>
     </row>
@@ -2348,32 +2348,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
           <t>56</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr">
         <is>
           <t>44</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>71</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -2401,32 +2401,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>53768</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>38015</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>48246</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>39143</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>30574</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>47654</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>53768</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>38015</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>49998</t>
+          <t>49589</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2441,7 +2441,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>97652</t>
+          <t>97836</t>
         </is>
       </c>
     </row>
@@ -2454,47 +2454,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>33082; 43802</t>
+          <t>47044; 59503</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>24543; 37013</t>
+          <t>31729; 44353</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>40517; 54912</t>
+          <t>41200; 54791</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>46972; 59598</t>
+          <t>32870; 44225</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>31298; 44610</t>
+          <t>24038; 37069</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>42412; 56704</t>
+          <t>41528; 56079</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>84885; 101071</t>
+          <t>84075; 100570</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>59408; 77940</t>
+          <t>58956; 77722</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>86817; 106875</t>
+          <t>87659; 106971</t>
         </is>
       </c>
     </row>
@@ -2511,32 +2511,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>624</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>536</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>593</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>632</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>528</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>579</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>624</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>536</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>593</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -2564,32 +2564,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>436278</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>373275</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>416488</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
           <t>435172</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>354691</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>409433</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>436278</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>373275</t>
-        </is>
-      </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>441693</t>
+          <t>385629</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>851125</t>
+          <t>802117</t>
         </is>
       </c>
     </row>
@@ -2617,47 +2617,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>416347; 454272</t>
+          <t>415338; 458761</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>334324; 376590</t>
+          <t>353121; 396872</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>383252; 442254</t>
+          <t>389189; 439114</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>414658; 456071</t>
+          <t>413256; 453726</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>352865; 397513</t>
+          <t>333343; 374832</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>412248; 469504</t>
+          <t>364731; 405541</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>841834; 899829</t>
+          <t>840121; 899796</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>695222; 758317</t>
+          <t>695989; 760820</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>813924; 893701</t>
+          <t>768300; 832394</t>
         </is>
       </c>
     </row>
